--- a/data/taste-answer-key.xlsx
+++ b/data/taste-answer-key.xlsx
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C21" s="65" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="65" t="n">
         <v>5</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C33" s="65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" s="65" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C34" s="66" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D34" s="66" t="n">
         <v>0</v>
